--- a/数据/无人机应急物资运输基础数据/通信链路参数.xlsx
+++ b/数据/无人机应急物资运输基础数据/通信链路参数.xlsx
@@ -1,18 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SF_Dir\第二十三届中国研究生数学建模竞赛 - 中文题目\中文题目\D题\数据\无人机应急物资运输基础数据\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
-    <sheet name="通信系统与端点参数 " sheetId="1" r:id="rId1"/>
+    <sheet name="数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <r>
       <rPr>
@@ -41,6 +36,17 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
+      <t>通信系统与端点参数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
       <t>参数类别</t>
     </r>
   </si>
@@ -144,12 +150,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t>L</t>
     </r>
     <r>
@@ -190,12 +190,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t>L</t>
     </r>
     <r>
@@ -246,12 +240,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t>P</t>
     </r>
     <r>
@@ -331,12 +319,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t>P</t>
     </r>
     <r>
@@ -444,12 +426,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t>h</t>
     </r>
     <r>
@@ -626,17 +602,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <i/>
       <sz val="8"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <name val="SimSun"/>
@@ -843,7 +819,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -855,9 +831,18 @@
       <left style="thin">
         <color rgb="FFA6A6A6"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color rgb="FFA6A6A6"/>
-      </right>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFA6A6A6"/>
       </top>
@@ -870,7 +855,9 @@
       <left style="thin">
         <color rgb="FFA6A6A6"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
       <top style="thin">
         <color rgb="FFA6A6A6"/>
       </top>
@@ -1016,7 +1003,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1028,34 +1015,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1141,34 +1128,37 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
@@ -1643,8 +1633,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
@@ -1657,235 +1647,244 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:5">
-      <c r="A2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="9">
-        <v>2400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="10">
-        <v>3</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:5">
-      <c r="A4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="10">
-        <v>10</v>
+      <c r="E4" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="10">
-        <v>-98</v>
+      <c r="E5" s="11">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="10">
-        <v>8</v>
+      <c r="E6" s="11">
+        <v>-98</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="10">
-        <v>20</v>
+      <c r="E7" s="11">
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5">
-      <c r="A8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="11">
         <v>20</v>
-      </c>
-      <c r="E8" s="10">
-        <v>3</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="10">
-        <v>20</v>
+      <c r="E9" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5">
-      <c r="A10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="11">
         <v>20</v>
-      </c>
-      <c r="E10" s="10">
-        <v>6</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="10">
-        <v>19</v>
+      <c r="B11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5">
-      <c r="A12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="10">
-        <v>8</v>
+      <c r="E12" s="11">
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="10">
-        <v>27</v>
+      <c r="B13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="11">
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5">
-      <c r="A14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="A14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="10">
-        <v>12</v>
+      <c r="E14" s="11">
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:5">
-      <c r="A15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8" t="s">
+      <c r="B15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:5">
+      <c r="A16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="10">
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="11">
         <v>20</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1" spans="1:5">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+    <row r="17" ht="22.5" customHeight="1" spans="2:4">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1:C1"/>
+  <mergeCells count="16">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -1900,6 +1899,7 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
